--- a/Documentacion Sprint (01 - 11)/Sprint 9 documentacion/Sprint_09_Backlog_ICARO.xlsx
+++ b/Documentacion Sprint (01 - 11)/Sprint 9 documentacion/Sprint_09_Backlog_ICARO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 9 documentacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentacion Sprint (01 - 11)\Sprint 9 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D93F8E8-D3E0-409B-A75F-7049E19CE628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A598328E-4C6E-4738-B7B2-F2A07A1AC7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SPRINT BACLOG" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="244">
   <si>
     <t>ID</t>
   </si>
@@ -1104,13 +1104,16 @@
   </si>
   <si>
     <t>9</t>
+  </si>
+  <si>
+    <t>Los estados presentados en este documento corresponden al estado del Product/Sprint Backlog al cierre del Sprint respectivo. Debido a la naturaleza iterativa e incremental del proyecto, los elementos identificados como pendientes, diferidos o parcialmente implementados pudieron ser desarrollados y completados en sprints posteriores. Para conocer el estado definitivo de cada historia de usuario o historia técnica, debe consultarse el Product Backlog Consolidado al cierre del proyecto.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1211,8 +1214,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1261,8 +1271,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1394,11 +1409,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1493,38 +1524,38 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1536,9 +1567,13 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Notas" xfId="1" builtinId="10"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
@@ -1978,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB3AEE0-C164-4706-BF72-3C1DE6FD46E5}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="17.5703125" customWidth="1"/>
@@ -1989,7 +2024,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="40" t="s">
         <v>241</v>
       </c>
       <c r="B1" s="33"/>
@@ -2005,7 +2040,7 @@
       <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="41" t="s">
         <v>127</v>
       </c>
       <c r="B2" s="33"/>
@@ -2024,51 +2059,51 @@
       <c r="A3" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
       <c r="G3" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
     </row>
     <row r="4" spans="1:12" ht="24">
       <c r="A4" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="39">
+      <c r="B4" s="42">
         <v>46181</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H4" s="39">
+      <c r="H4" s="42">
         <v>46185</v>
       </c>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
     </row>
     <row r="5" spans="1:12" ht="99.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="32" t="s">
         <v>134</v>
       </c>
       <c r="C5" s="33"/>
@@ -2078,35 +2113,35 @@
       <c r="G5" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="H5" s="35" t="s">
+      <c r="H5" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
     </row>
     <row r="6" spans="1:12" ht="24">
       <c r="A6" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
       <c r="G6" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="H6" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
     </row>
     <row r="7" spans="1:12" ht="30">
       <c r="A7" s="5" t="s">
@@ -2337,13 +2372,13 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
       <c r="F13" s="7">
         <v>35</v>
       </c>
@@ -2356,19 +2391,85 @@
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
     </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="47" t="s">
+        <v>243</v>
+      </c>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="47"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="47"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="A13:E13"/>
+  <mergeCells count="12">
+    <mergeCell ref="A16:G22"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:L4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
